--- a/youzi/中信总部/index.xlsx
+++ b/youzi/中信总部/index.xlsx
@@ -39,18 +39,66 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF7D3D7"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF7D3D7"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFCF0F1"/>
         <bgColor/>
       </patternFill>
@@ -69,13 +117,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDFEFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9ED7AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED19D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -87,31 +171,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
+        <fgColor rgb="FFFEF9FA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,19 +189,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9ED7AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ED19D"/>
+        <fgColor rgb="FFF7D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -147,54 +243,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDFEFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9FA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -225,427 +273,379 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF6CED1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF4C3C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3606D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3CAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA3D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4251"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9CD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C3C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C87"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3606D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C3C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4251"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9CD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA3D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3CAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C87"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C3C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2026,7 +2026,7 @@
       <c r="C2" t="str">
         <v>601107</v>
       </c>
-      <c r="D2" s="8" t="str">
+      <c r="D2" s="3" t="str">
         <v>净买: 2386.11万</v>
       </c>
       <c r="E2">
@@ -2041,40 +2041,40 @@
       <c r="H2">
         <v>-0.18</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="11">
         <v>0.36</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2" s="4">
         <v>1.07</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="8">
         <v>0.18</v>
       </c>
-      <c r="L2" s="13">
+      <c r="L2" s="9">
         <v>0.18</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2" s="12">
         <v>-0.54</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="5">
         <v>0.36</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="13">
         <v>0.18</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="10">
         <v>1.07</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="6">
         <v>1.07</v>
       </c>
-      <c r="R2" s="11">
+      <c r="R2" s="7">
         <v>0.89</v>
       </c>
-      <c r="S2" s="6">
+      <c r="S2" s="1">
         <v>1.61</v>
       </c>
-      <c r="T2" s="7">
+      <c r="T2" s="2">
         <v>7.32</v>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       <c r="C3" t="str">
         <v>688755</v>
       </c>
-      <c r="D3" s="18" t="str">
+      <c r="D3" s="22" t="str">
         <v>净买: 1006.54万</v>
       </c>
       <c r="E3">
@@ -2103,40 +2103,40 @@
       <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="16">
         <v>-0.04</v>
       </c>
-      <c r="J3" s="15">
+      <c r="J3" s="19">
         <v>1.4</v>
       </c>
-      <c r="K3" s="24">
+      <c r="K3" s="26">
         <v>1.01</v>
       </c>
-      <c r="L3" s="25">
+      <c r="L3" s="17">
         <v>2.08</v>
       </c>
-      <c r="M3" s="20">
+      <c r="M3" s="23">
         <v>0.13</v>
       </c>
-      <c r="N3" s="21">
+      <c r="N3" s="24">
         <v>0.11</v>
       </c>
-      <c r="O3" s="22">
+      <c r="O3" s="14">
         <v>-0.48</v>
       </c>
-      <c r="P3" s="16">
+      <c r="P3" s="18">
         <v>-2.25</v>
       </c>
-      <c r="Q3" s="17">
+      <c r="Q3" s="20">
         <v>-2.61</v>
       </c>
-      <c r="R3" s="23">
+      <c r="R3" s="21">
         <v>-2.15</v>
       </c>
-      <c r="S3" s="26">
+      <c r="S3" s="15">
         <v>-2.01</v>
       </c>
-      <c r="T3" s="14">
+      <c r="T3" s="25">
         <v>-15.65</v>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       <c r="C4" t="str">
         <v>688719</v>
       </c>
-      <c r="D4" s="32" t="str">
+      <c r="D4" s="34" t="str">
         <v>净买: 9087.83万</v>
       </c>
       <c r="E4">
@@ -2165,40 +2165,40 @@
       <c r="H4">
         <v>-1.27</v>
       </c>
-      <c r="I4" s="37">
+      <c r="I4" s="32">
         <v>14.77</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="35">
         <v>16.43</v>
       </c>
-      <c r="K4" s="33">
+      <c r="K4" s="36">
         <v>15.22</v>
       </c>
       <c r="L4" s="38">
         <v>19.4</v>
       </c>
-      <c r="M4" s="29">
+      <c r="M4" s="39">
         <v>29.05</v>
       </c>
-      <c r="N4" s="30">
+      <c r="N4" s="27">
         <v>28.01</v>
       </c>
-      <c r="O4" s="39">
+      <c r="O4" s="33">
         <v>5.89</v>
       </c>
-      <c r="P4" s="34">
+      <c r="P4" s="30">
         <v>21.83</v>
       </c>
-      <c r="Q4" s="35">
+      <c r="Q4" s="37">
         <v>28.6</v>
       </c>
-      <c r="R4" s="31">
+      <c r="R4" s="28">
         <v>16.64</v>
       </c>
-      <c r="S4" s="36">
+      <c r="S4" s="29">
         <v>10.06</v>
       </c>
-      <c r="T4" s="27">
+      <c r="T4" s="31">
         <v>41.76</v>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="C5" t="str">
         <v>603496</v>
       </c>
-      <c r="D5" s="46" t="str">
+      <c r="D5" s="51" t="str">
         <v>净买: 3657.24万</v>
       </c>
       <c r="E5">
@@ -2227,40 +2227,40 @@
       <c r="H5">
         <v>10.01</v>
       </c>
-      <c r="I5" s="41">
+      <c r="I5" s="52">
         <v>0</v>
       </c>
-      <c r="J5" s="49">
+      <c r="J5" s="40">
         <v>1.21</v>
       </c>
-      <c r="K5" s="44">
+      <c r="K5" s="45">
         <v>8.48</v>
       </c>
-      <c r="L5" s="50">
+      <c r="L5" s="49">
         <v>-2.37</v>
       </c>
-      <c r="M5" s="45">
+      <c r="M5" s="46">
         <v>-7.81</v>
       </c>
-      <c r="N5" s="42">
+      <c r="N5" s="41">
         <v>-10.99</v>
       </c>
-      <c r="O5" s="43">
+      <c r="O5" s="47">
         <v>-12.99</v>
       </c>
-      <c r="P5" s="51">
+      <c r="P5" s="42">
         <v>-13.07</v>
       </c>
-      <c r="Q5" s="52">
+      <c r="Q5" s="48">
         <v>-13.38</v>
       </c>
-      <c r="R5" s="47">
+      <c r="R5" s="43">
         <v>-11.41</v>
       </c>
-      <c r="S5" s="40">
+      <c r="S5" s="50">
         <v>-13.52</v>
       </c>
-      <c r="T5" s="48">
+      <c r="T5" s="44">
         <v>-15.75</v>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       <c r="C6" t="str">
         <v>600307</v>
       </c>
-      <c r="D6" s="63" t="str">
+      <c r="D6" s="60" t="str">
         <v>净买: 502.19万</v>
       </c>
       <c r="E6">
@@ -2289,40 +2289,40 @@
       <c r="H6">
         <v>2</v>
       </c>
-      <c r="I6" s="59">
+      <c r="I6" s="58">
         <v>7.84</v>
       </c>
-      <c r="J6" s="60">
+      <c r="J6" s="59">
         <v>18.63</v>
       </c>
-      <c r="K6" s="57">
+      <c r="K6" s="54">
         <v>11.76</v>
       </c>
-      <c r="L6" s="64">
+      <c r="L6" s="61">
         <v>4.41</v>
       </c>
-      <c r="M6" s="65">
+      <c r="M6" s="55">
         <v>1.47</v>
       </c>
-      <c r="N6" s="53">
+      <c r="N6" s="56">
         <v>5.88</v>
       </c>
-      <c r="O6" s="61">
+      <c r="O6" s="62">
         <v>6.86</v>
       </c>
-      <c r="P6" s="62">
+      <c r="P6" s="63">
         <v>2.45</v>
       </c>
-      <c r="Q6" s="54">
+      <c r="Q6" s="65">
         <v>4.41</v>
       </c>
-      <c r="R6" s="55">
+      <c r="R6" s="64">
         <v>3.92</v>
       </c>
-      <c r="S6" s="56">
+      <c r="S6" s="57">
         <v>-1.47</v>
       </c>
-      <c r="T6" s="58">
+      <c r="T6" s="53">
         <v>-11.27</v>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       <c r="C7" t="str">
         <v>688566</v>
       </c>
-      <c r="D7" s="67" t="str">
+      <c r="D7" s="70" t="str">
         <v>净买: 36.33万</v>
       </c>
       <c r="E7">
@@ -2351,40 +2351,40 @@
       <c r="H7">
         <v>-1.02</v>
       </c>
-      <c r="I7" s="74">
+      <c r="I7" s="71">
         <v>-0.57</v>
       </c>
-      <c r="J7" s="68">
+      <c r="J7" s="72">
         <v>-1.27</v>
       </c>
-      <c r="K7" s="78">
+      <c r="K7" s="73">
         <v>-6.47</v>
       </c>
-      <c r="L7" s="76">
+      <c r="L7" s="66">
         <v>-4.53</v>
       </c>
-      <c r="M7" s="69">
+      <c r="M7" s="68">
         <v>-3.73</v>
       </c>
-      <c r="N7" s="77">
+      <c r="N7" s="69">
         <v>-4</v>
       </c>
-      <c r="O7" s="70">
+      <c r="O7" s="67">
         <v>-1.03</v>
       </c>
-      <c r="P7" s="71">
+      <c r="P7" s="77">
         <v>-2.3</v>
       </c>
-      <c r="Q7" s="72">
+      <c r="Q7" s="74">
         <v>-2.13</v>
       </c>
-      <c r="R7" s="66">
+      <c r="R7" s="75">
         <v>4.67</v>
       </c>
-      <c r="S7" s="73">
+      <c r="S7" s="76">
         <v>8.87</v>
       </c>
-      <c r="T7" s="75">
+      <c r="T7" s="78">
         <v>4.33</v>
       </c>
     </row>
@@ -2447,40 +2447,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="87">
+      <c r="I9" s="84">
         <v>50</v>
       </c>
-      <c r="J9" s="88">
+      <c r="J9" s="87">
         <v>83.33</v>
       </c>
-      <c r="K9" s="79">
+      <c r="K9" s="85">
         <v>83.33</v>
       </c>
-      <c r="L9" s="90">
+      <c r="L9" s="89">
         <v>66.67</v>
       </c>
-      <c r="M9" s="83">
+      <c r="M9" s="79">
         <v>50</v>
       </c>
-      <c r="N9" s="89">
+      <c r="N9" s="80">
         <v>66.67</v>
       </c>
-      <c r="O9" s="84">
+      <c r="O9" s="81">
         <v>50</v>
       </c>
-      <c r="P9" s="85">
+      <c r="P9" s="82">
         <v>50</v>
       </c>
-      <c r="Q9" s="80">
+      <c r="Q9" s="90">
         <v>50</v>
       </c>
-      <c r="R9" s="81">
+      <c r="R9" s="83">
         <v>66.67</v>
       </c>
       <c r="S9" s="86">
         <v>50</v>
       </c>
-      <c r="T9" s="82">
+      <c r="T9" s="88">
         <v>50</v>
       </c>
     </row>
@@ -2495,40 +2495,40 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="102">
+      <c r="I10" s="97">
         <v>3.73</v>
       </c>
-      <c r="J10" s="99">
+      <c r="J10" s="101">
         <v>6.24</v>
       </c>
-      <c r="K10" s="91">
+      <c r="K10" s="92">
         <v>5.03</v>
       </c>
-      <c r="L10" s="92">
+      <c r="L10" s="93">
         <v>3.2</v>
       </c>
-      <c r="M10" s="100">
+      <c r="M10" s="98">
         <v>3.1</v>
       </c>
-      <c r="N10" s="97">
+      <c r="N10" s="99">
         <v>3.23</v>
       </c>
-      <c r="O10" s="93">
+      <c r="O10" s="94">
         <v>-0.26</v>
       </c>
-      <c r="P10" s="94">
+      <c r="P10" s="100">
         <v>1.29</v>
       </c>
-      <c r="Q10" s="95">
+      <c r="Q10" s="102">
         <v>2.66</v>
       </c>
-      <c r="R10" s="98">
+      <c r="R10" s="96">
         <v>2.09</v>
       </c>
-      <c r="S10" s="96">
+      <c r="S10" s="95">
         <v>0.59</v>
       </c>
-      <c r="T10" s="101">
+      <c r="T10" s="91">
         <v>1.79</v>
       </c>
     </row>

--- a/youzi/中信总部/index.xlsx
+++ b/youzi/中信总部/index.xlsx
@@ -39,12 +39,60 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF3BDC3"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC32938"/>
         <bgColor/>
       </patternFill>
@@ -63,55 +111,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF8DBDD"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
+        <fgColor rgb="FF9ED7AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF9FA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,7 +171,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
+        <fgColor rgb="FF8ED19D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -141,25 +195,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF9ED7AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ED19D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -171,13 +213,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9FA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -189,7 +279,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7D6D9"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CED1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -207,6 +369,204 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3606D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C3C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA3D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4251"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3CAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9CD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -219,433 +579,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C3C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE87C87"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C3C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3606D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3CAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA3D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4251"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9CD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C3C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C87"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2026,7 +2026,7 @@
       <c r="C2" t="str">
         <v>601107</v>
       </c>
-      <c r="D2" s="3" t="str">
+      <c r="D2" s="11" t="str">
         <v>净买: 2386.11万</v>
       </c>
       <c r="E2">
@@ -2041,40 +2041,40 @@
       <c r="H2">
         <v>-0.18</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="2">
         <v>0.36</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="1">
         <v>1.07</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2" s="3">
         <v>0.18</v>
       </c>
-      <c r="L2" s="9">
+      <c r="L2" s="6">
         <v>0.18</v>
       </c>
-      <c r="M2" s="12">
+      <c r="M2" s="7">
         <v>-0.54</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="4">
         <v>0.36</v>
       </c>
-      <c r="O2" s="13">
+      <c r="O2" s="8">
         <v>0.18</v>
       </c>
-      <c r="P2" s="10">
+      <c r="P2" s="9">
         <v>1.07</v>
       </c>
-      <c r="Q2" s="6">
+      <c r="Q2" s="12">
         <v>1.07</v>
       </c>
-      <c r="R2" s="7">
+      <c r="R2" s="13">
         <v>0.89</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="5">
         <v>1.61</v>
       </c>
-      <c r="T2" s="2">
+      <c r="T2" s="10">
         <v>7.32</v>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       <c r="C3" t="str">
         <v>688755</v>
       </c>
-      <c r="D3" s="22" t="str">
+      <c r="D3" s="24" t="str">
         <v>净买: 1006.54万</v>
       </c>
       <c r="E3">
@@ -2103,40 +2103,40 @@
       <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="25">
         <v>-0.04</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="17">
         <v>1.4</v>
       </c>
-      <c r="K3" s="26">
+      <c r="K3" s="18">
         <v>1.01</v>
       </c>
-      <c r="L3" s="17">
+      <c r="L3" s="26">
         <v>2.08</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="15">
         <v>0.13</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="19">
         <v>0.11</v>
       </c>
-      <c r="O3" s="14">
+      <c r="O3" s="22">
         <v>-0.48</v>
       </c>
-      <c r="P3" s="18">
+      <c r="P3" s="14">
         <v>-2.25</v>
       </c>
-      <c r="Q3" s="20">
+      <c r="Q3" s="23">
         <v>-2.61</v>
       </c>
-      <c r="R3" s="21">
+      <c r="R3" s="20">
         <v>-2.15</v>
       </c>
-      <c r="S3" s="15">
+      <c r="S3" s="21">
         <v>-2.01</v>
       </c>
-      <c r="T3" s="25">
+      <c r="T3" s="16">
         <v>-15.65</v>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       <c r="C4" t="str">
         <v>688719</v>
       </c>
-      <c r="D4" s="34" t="str">
+      <c r="D4" s="29" t="str">
         <v>净买: 9087.83万</v>
       </c>
       <c r="E4">
@@ -2165,40 +2165,40 @@
       <c r="H4">
         <v>-1.27</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="34">
         <v>14.77</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="31">
         <v>16.43</v>
       </c>
-      <c r="K4" s="36">
+      <c r="K4" s="39">
         <v>15.22</v>
       </c>
-      <c r="L4" s="38">
+      <c r="L4" s="32">
         <v>19.4</v>
       </c>
-      <c r="M4" s="39">
+      <c r="M4" s="27">
         <v>29.05</v>
       </c>
-      <c r="N4" s="27">
+      <c r="N4" s="35">
         <v>28.01</v>
       </c>
-      <c r="O4" s="33">
+      <c r="O4" s="36">
         <v>5.89</v>
       </c>
-      <c r="P4" s="30">
+      <c r="P4" s="33">
         <v>21.83</v>
       </c>
       <c r="Q4" s="37">
         <v>28.6</v>
       </c>
-      <c r="R4" s="28">
+      <c r="R4" s="30">
         <v>16.64</v>
       </c>
-      <c r="S4" s="29">
+      <c r="S4" s="28">
         <v>10.06</v>
       </c>
-      <c r="T4" s="31">
+      <c r="T4" s="38">
         <v>41.76</v>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="C5" t="str">
         <v>603496</v>
       </c>
-      <c r="D5" s="51" t="str">
+      <c r="D5" s="44" t="str">
         <v>净买: 3657.24万</v>
       </c>
       <c r="E5">
@@ -2227,40 +2227,40 @@
       <c r="H5">
         <v>10.01</v>
       </c>
-      <c r="I5" s="52">
+      <c r="I5" s="42">
         <v>0</v>
       </c>
-      <c r="J5" s="40">
+      <c r="J5" s="51">
         <v>1.21</v>
       </c>
       <c r="K5" s="45">
         <v>8.48</v>
       </c>
-      <c r="L5" s="49">
+      <c r="L5" s="52">
         <v>-2.37</v>
       </c>
-      <c r="M5" s="46">
+      <c r="M5" s="43">
         <v>-7.81</v>
       </c>
-      <c r="N5" s="41">
+      <c r="N5" s="46">
         <v>-10.99</v>
       </c>
-      <c r="O5" s="47">
+      <c r="O5" s="40">
         <v>-12.99</v>
       </c>
-      <c r="P5" s="42">
+      <c r="P5" s="47">
         <v>-13.07</v>
       </c>
-      <c r="Q5" s="48">
+      <c r="Q5" s="41">
         <v>-13.38</v>
       </c>
-      <c r="R5" s="43">
+      <c r="R5" s="48">
         <v>-11.41</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="49">
         <v>-13.52</v>
       </c>
-      <c r="T5" s="44">
+      <c r="T5" s="50">
         <v>-15.75</v>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       <c r="C6" t="str">
         <v>600307</v>
       </c>
-      <c r="D6" s="60" t="str">
+      <c r="D6" s="57" t="str">
         <v>净买: 502.19万</v>
       </c>
       <c r="E6">
@@ -2289,37 +2289,37 @@
       <c r="H6">
         <v>2</v>
       </c>
-      <c r="I6" s="58">
+      <c r="I6" s="62">
         <v>7.84</v>
       </c>
-      <c r="J6" s="59">
+      <c r="J6" s="54">
         <v>18.63</v>
       </c>
-      <c r="K6" s="54">
+      <c r="K6" s="55">
         <v>11.76</v>
       </c>
       <c r="L6" s="61">
         <v>4.41</v>
       </c>
-      <c r="M6" s="55">
+      <c r="M6" s="63">
         <v>1.47</v>
       </c>
-      <c r="N6" s="56">
+      <c r="N6" s="64">
         <v>5.88</v>
       </c>
-      <c r="O6" s="62">
+      <c r="O6" s="58">
         <v>6.86</v>
       </c>
-      <c r="P6" s="63">
+      <c r="P6" s="65">
         <v>2.45</v>
       </c>
-      <c r="Q6" s="65">
+      <c r="Q6" s="59">
         <v>4.41</v>
       </c>
-      <c r="R6" s="64">
+      <c r="R6" s="60">
         <v>3.92</v>
       </c>
-      <c r="S6" s="57">
+      <c r="S6" s="56">
         <v>-1.47</v>
       </c>
       <c r="T6" s="53">
@@ -2336,7 +2336,7 @@
       <c r="C7" t="str">
         <v>688566</v>
       </c>
-      <c r="D7" s="70" t="str">
+      <c r="D7" s="76" t="str">
         <v>净买: 36.33万</v>
       </c>
       <c r="E7">
@@ -2351,40 +2351,40 @@
       <c r="H7">
         <v>-1.02</v>
       </c>
-      <c r="I7" s="71">
+      <c r="I7" s="73">
         <v>-0.57</v>
       </c>
-      <c r="J7" s="72">
+      <c r="J7" s="77">
         <v>-1.27</v>
       </c>
-      <c r="K7" s="73">
+      <c r="K7" s="71">
         <v>-6.47</v>
       </c>
-      <c r="L7" s="66">
+      <c r="L7" s="72">
         <v>-4.53</v>
       </c>
-      <c r="M7" s="68">
+      <c r="M7" s="70">
         <v>-3.73</v>
       </c>
-      <c r="N7" s="69">
+      <c r="N7" s="78">
         <v>-4</v>
       </c>
-      <c r="O7" s="67">
+      <c r="O7" s="74">
         <v>-1.03</v>
       </c>
-      <c r="P7" s="77">
+      <c r="P7" s="75">
         <v>-2.3</v>
       </c>
-      <c r="Q7" s="74">
+      <c r="Q7" s="66">
         <v>-2.13</v>
       </c>
-      <c r="R7" s="75">
+      <c r="R7" s="67">
         <v>4.67</v>
       </c>
-      <c r="S7" s="76">
+      <c r="S7" s="68">
         <v>8.87</v>
       </c>
-      <c r="T7" s="78">
+      <c r="T7" s="69">
         <v>4.33</v>
       </c>
     </row>
@@ -2447,40 +2447,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="84">
+      <c r="I9" s="82">
         <v>50</v>
       </c>
-      <c r="J9" s="87">
+      <c r="J9" s="89">
         <v>83.33</v>
       </c>
-      <c r="K9" s="85">
+      <c r="K9" s="90">
         <v>83.33</v>
       </c>
-      <c r="L9" s="89">
+      <c r="L9" s="83">
         <v>66.67</v>
       </c>
-      <c r="M9" s="79">
+      <c r="M9" s="85">
         <v>50</v>
       </c>
-      <c r="N9" s="80">
+      <c r="N9" s="79">
         <v>66.67</v>
       </c>
-      <c r="O9" s="81">
+      <c r="O9" s="86">
         <v>50</v>
       </c>
-      <c r="P9" s="82">
+      <c r="P9" s="80">
         <v>50</v>
       </c>
-      <c r="Q9" s="90">
+      <c r="Q9" s="87">
         <v>50</v>
       </c>
-      <c r="R9" s="83">
+      <c r="R9" s="84">
         <v>66.67</v>
       </c>
-      <c r="S9" s="86">
+      <c r="S9" s="88">
         <v>50</v>
       </c>
-      <c r="T9" s="88">
+      <c r="T9" s="81">
         <v>50</v>
       </c>
     </row>
@@ -2495,40 +2495,40 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="97">
+      <c r="I10" s="96">
         <v>3.73</v>
       </c>
-      <c r="J10" s="101">
+      <c r="J10" s="102">
         <v>6.24</v>
       </c>
-      <c r="K10" s="92">
+      <c r="K10" s="97">
         <v>5.03</v>
       </c>
-      <c r="L10" s="93">
+      <c r="L10" s="91">
         <v>3.2</v>
       </c>
-      <c r="M10" s="98">
+      <c r="M10" s="92">
         <v>3.1</v>
       </c>
-      <c r="N10" s="99">
+      <c r="N10" s="93">
         <v>3.23</v>
       </c>
       <c r="O10" s="94">
         <v>-0.26</v>
       </c>
-      <c r="P10" s="100">
+      <c r="P10" s="98">
         <v>1.29</v>
       </c>
-      <c r="Q10" s="102">
+      <c r="Q10" s="99">
         <v>2.66</v>
       </c>
-      <c r="R10" s="96">
+      <c r="R10" s="100">
         <v>2.09</v>
       </c>
       <c r="S10" s="95">
         <v>0.59</v>
       </c>
-      <c r="T10" s="91">
+      <c r="T10" s="101">
         <v>1.79</v>
       </c>
     </row>

--- a/youzi/中信总部/index.xlsx
+++ b/youzi/中信总部/index.xlsx
@@ -45,6 +45,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFCF0F1"/>
         <bgColor/>
       </patternFill>
@@ -57,43 +81,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFCF0F1"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFDF7F8"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED19D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -105,13 +141,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDD"/>
+        <fgColor rgb="FFFDFEFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF9FA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,55 +171,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9FA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF7D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF5C6CA"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ED19D"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -183,18 +243,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDFEFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -207,12 +255,108 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CED1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -225,6 +369,180 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3606D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C3C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9CD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA3D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4251"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3CAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -237,355 +555,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C3C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3606D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C3C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA3D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4251"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3CAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9CD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -597,55 +639,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C3C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE87C87"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2041,41 +2041,41 @@
       <c r="H2">
         <v>-0.18</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="6">
         <v>0.36</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="9">
         <v>1.07</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="7">
         <v>0.18</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="4">
         <v>0.18</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="10">
         <v>-0.54</v>
       </c>
-      <c r="N2" s="4">
+      <c r="N2" s="12">
         <v>0.36</v>
       </c>
-      <c r="O2" s="8">
+      <c r="O2" s="13">
         <v>0.18</v>
       </c>
-      <c r="P2" s="9">
+      <c r="P2" s="1">
         <v>1.07</v>
       </c>
-      <c r="Q2" s="12">
+      <c r="Q2" s="2">
         <v>1.07</v>
       </c>
-      <c r="R2" s="13">
+      <c r="R2" s="3">
         <v>0.89</v>
       </c>
-      <c r="S2" s="5">
+      <c r="S2" s="8">
         <v>1.61</v>
       </c>
-      <c r="T2" s="10">
-        <v>7.32</v>
+      <c r="T2" s="5">
+        <v>8.75</v>
       </c>
     </row>
     <row r="3">
@@ -2088,7 +2088,7 @@
       <c r="C3" t="str">
         <v>688755</v>
       </c>
-      <c r="D3" s="24" t="str">
+      <c r="D3" s="17" t="str">
         <v>净买: 1006.54万</v>
       </c>
       <c r="E3">
@@ -2103,41 +2103,41 @@
       <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="18">
         <v>-0.04</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="26">
         <v>1.4</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K3" s="24">
         <v>1.01</v>
       </c>
-      <c r="L3" s="26">
+      <c r="L3" s="21">
         <v>2.08</v>
       </c>
-      <c r="M3" s="15">
+      <c r="M3" s="19">
         <v>0.13</v>
       </c>
-      <c r="N3" s="19">
+      <c r="N3" s="14">
         <v>0.11</v>
       </c>
-      <c r="O3" s="22">
+      <c r="O3" s="25">
         <v>-0.48</v>
       </c>
-      <c r="P3" s="14">
+      <c r="P3" s="22">
         <v>-2.25</v>
       </c>
-      <c r="Q3" s="23">
+      <c r="Q3" s="15">
         <v>-2.61</v>
       </c>
-      <c r="R3" s="20">
+      <c r="R3" s="16">
         <v>-2.15</v>
       </c>
-      <c r="S3" s="21">
+      <c r="S3" s="20">
         <v>-2.01</v>
       </c>
-      <c r="T3" s="16">
-        <v>-15.65</v>
+      <c r="T3" s="23">
+        <v>-15.61</v>
       </c>
     </row>
     <row r="4">
@@ -2150,7 +2150,7 @@
       <c r="C4" t="str">
         <v>688719</v>
       </c>
-      <c r="D4" s="29" t="str">
+      <c r="D4" s="34" t="str">
         <v>净买: 9087.83万</v>
       </c>
       <c r="E4">
@@ -2165,41 +2165,41 @@
       <c r="H4">
         <v>-1.27</v>
       </c>
-      <c r="I4" s="34">
+      <c r="I4" s="35">
         <v>14.77</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="39">
         <v>16.43</v>
       </c>
-      <c r="K4" s="39">
+      <c r="K4" s="36">
         <v>15.22</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4" s="28">
         <v>19.4</v>
       </c>
-      <c r="M4" s="27">
+      <c r="M4" s="37">
         <v>29.05</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="38">
         <v>28.01</v>
       </c>
-      <c r="O4" s="36">
+      <c r="O4" s="29">
         <v>5.89</v>
       </c>
-      <c r="P4" s="33">
+      <c r="P4" s="30">
         <v>21.83</v>
       </c>
-      <c r="Q4" s="37">
+      <c r="Q4" s="27">
         <v>28.6</v>
       </c>
-      <c r="R4" s="30">
+      <c r="R4" s="32">
         <v>16.64</v>
       </c>
-      <c r="S4" s="28">
+      <c r="S4" s="33">
         <v>10.06</v>
       </c>
-      <c r="T4" s="38">
-        <v>41.76</v>
+      <c r="T4" s="31">
+        <v>45.75</v>
       </c>
     </row>
     <row r="5">
@@ -2212,7 +2212,7 @@
       <c r="C5" t="str">
         <v>603496</v>
       </c>
-      <c r="D5" s="44" t="str">
+      <c r="D5" s="52" t="str">
         <v>净买: 3657.24万</v>
       </c>
       <c r="E5">
@@ -2227,41 +2227,41 @@
       <c r="H5">
         <v>10.01</v>
       </c>
-      <c r="I5" s="42">
+      <c r="I5" s="40">
         <v>0</v>
       </c>
-      <c r="J5" s="51">
+      <c r="J5" s="44">
         <v>1.21</v>
       </c>
-      <c r="K5" s="45">
+      <c r="K5" s="47">
         <v>8.48</v>
       </c>
-      <c r="L5" s="52">
+      <c r="L5" s="41">
         <v>-2.37</v>
       </c>
-      <c r="M5" s="43">
+      <c r="M5" s="42">
         <v>-7.81</v>
       </c>
-      <c r="N5" s="46">
+      <c r="N5" s="48">
         <v>-10.99</v>
       </c>
-      <c r="O5" s="40">
+      <c r="O5" s="45">
         <v>-12.99</v>
       </c>
-      <c r="P5" s="47">
+      <c r="P5" s="49">
         <v>-13.07</v>
       </c>
-      <c r="Q5" s="41">
+      <c r="Q5" s="50">
         <v>-13.38</v>
       </c>
-      <c r="R5" s="48">
+      <c r="R5" s="43">
         <v>-11.41</v>
       </c>
-      <c r="S5" s="49">
+      <c r="S5" s="46">
         <v>-13.52</v>
       </c>
-      <c r="T5" s="50">
-        <v>-15.75</v>
+      <c r="T5" s="51">
+        <v>-16.17</v>
       </c>
     </row>
     <row r="6">
@@ -2274,7 +2274,7 @@
       <c r="C6" t="str">
         <v>600307</v>
       </c>
-      <c r="D6" s="57" t="str">
+      <c r="D6" s="59" t="str">
         <v>净买: 502.19万</v>
       </c>
       <c r="E6">
@@ -2289,7 +2289,7 @@
       <c r="H6">
         <v>2</v>
       </c>
-      <c r="I6" s="62">
+      <c r="I6" s="53">
         <v>7.84</v>
       </c>
       <c r="J6" s="54">
@@ -2298,32 +2298,32 @@
       <c r="K6" s="55">
         <v>11.76</v>
       </c>
-      <c r="L6" s="61">
+      <c r="L6" s="60">
         <v>4.41</v>
       </c>
-      <c r="M6" s="63">
+      <c r="M6" s="61">
         <v>1.47</v>
       </c>
-      <c r="N6" s="64">
+      <c r="N6" s="56">
         <v>5.88</v>
       </c>
-      <c r="O6" s="58">
+      <c r="O6" s="57">
         <v>6.86</v>
       </c>
-      <c r="P6" s="65">
+      <c r="P6" s="62">
         <v>2.45</v>
       </c>
-      <c r="Q6" s="59">
+      <c r="Q6" s="63">
         <v>4.41</v>
       </c>
-      <c r="R6" s="60">
+      <c r="R6" s="58">
         <v>3.92</v>
       </c>
-      <c r="S6" s="56">
+      <c r="S6" s="64">
         <v>-1.47</v>
       </c>
-      <c r="T6" s="53">
-        <v>-11.27</v>
+      <c r="T6" s="65">
+        <v>-10.78</v>
       </c>
     </row>
     <row r="7">
@@ -2336,7 +2336,7 @@
       <c r="C7" t="str">
         <v>688566</v>
       </c>
-      <c r="D7" s="76" t="str">
+      <c r="D7" s="73" t="str">
         <v>净买: 36.33万</v>
       </c>
       <c r="E7">
@@ -2351,41 +2351,41 @@
       <c r="H7">
         <v>-1.02</v>
       </c>
-      <c r="I7" s="73">
+      <c r="I7" s="74">
         <v>-0.57</v>
       </c>
-      <c r="J7" s="77">
+      <c r="J7" s="66">
         <v>-1.27</v>
       </c>
-      <c r="K7" s="71">
+      <c r="K7" s="75">
         <v>-6.47</v>
       </c>
-      <c r="L7" s="72">
+      <c r="L7" s="76">
         <v>-4.53</v>
       </c>
-      <c r="M7" s="70">
+      <c r="M7" s="77">
         <v>-3.73</v>
       </c>
-      <c r="N7" s="78">
+      <c r="N7" s="69">
         <v>-4</v>
       </c>
-      <c r="O7" s="74">
+      <c r="O7" s="78">
         <v>-1.03</v>
       </c>
-      <c r="P7" s="75">
+      <c r="P7" s="67">
         <v>-2.3</v>
       </c>
-      <c r="Q7" s="66">
+      <c r="Q7" s="68">
         <v>-2.13</v>
       </c>
-      <c r="R7" s="67">
+      <c r="R7" s="70">
         <v>4.67</v>
       </c>
-      <c r="S7" s="68">
+      <c r="S7" s="72">
         <v>8.87</v>
       </c>
-      <c r="T7" s="69">
-        <v>4.33</v>
+      <c r="T7" s="71">
+        <v>3.4</v>
       </c>
     </row>
     <row r="8">
@@ -2447,40 +2447,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="82">
+      <c r="I9" s="80">
         <v>50</v>
       </c>
-      <c r="J9" s="89">
+      <c r="J9" s="85">
         <v>83.33</v>
       </c>
-      <c r="K9" s="90">
+      <c r="K9" s="86">
         <v>83.33</v>
       </c>
-      <c r="L9" s="83">
+      <c r="L9" s="88">
         <v>66.67</v>
       </c>
-      <c r="M9" s="85">
+      <c r="M9" s="79">
         <v>50</v>
       </c>
-      <c r="N9" s="79">
+      <c r="N9" s="81">
         <v>66.67</v>
       </c>
-      <c r="O9" s="86">
+      <c r="O9" s="82">
         <v>50</v>
       </c>
-      <c r="P9" s="80">
+      <c r="P9" s="89">
         <v>50</v>
       </c>
-      <c r="Q9" s="87">
+      <c r="Q9" s="90">
         <v>50</v>
       </c>
-      <c r="R9" s="84">
+      <c r="R9" s="83">
         <v>66.67</v>
       </c>
-      <c r="S9" s="88">
+      <c r="S9" s="87">
         <v>50</v>
       </c>
-      <c r="T9" s="81">
+      <c r="T9" s="84">
         <v>50</v>
       </c>
     </row>
@@ -2495,41 +2495,41 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="96">
+      <c r="I10" s="93">
         <v>3.73</v>
       </c>
-      <c r="J10" s="102">
+      <c r="J10" s="94">
         <v>6.24</v>
       </c>
       <c r="K10" s="97">
         <v>5.03</v>
       </c>
-      <c r="L10" s="91">
+      <c r="L10" s="95">
         <v>3.2</v>
       </c>
-      <c r="M10" s="92">
+      <c r="M10" s="91">
         <v>3.1</v>
       </c>
-      <c r="N10" s="93">
+      <c r="N10" s="100">
         <v>3.23</v>
       </c>
-      <c r="O10" s="94">
+      <c r="O10" s="96">
         <v>-0.26</v>
       </c>
-      <c r="P10" s="98">
+      <c r="P10" s="101">
         <v>1.29</v>
       </c>
-      <c r="Q10" s="99">
+      <c r="Q10" s="98">
         <v>2.66</v>
       </c>
-      <c r="R10" s="100">
+      <c r="R10" s="102">
         <v>2.09</v>
       </c>
-      <c r="S10" s="95">
+      <c r="S10" s="92">
         <v>0.59</v>
       </c>
-      <c r="T10" s="101">
-        <v>1.79</v>
+      <c r="T10" s="99">
+        <v>2.56</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/中信总部/index.xlsx
+++ b/youzi/中信总部/index.xlsx
@@ -39,12 +39,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF7D3D7"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF7D3D7"/>
         <bgColor/>
       </patternFill>
@@ -57,43 +75,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFDF7F8"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFDF7F8"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF7D3D7"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -105,13 +117,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDFEFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF9FA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9ED7AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED19D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,49 +183,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF8ED19D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDFEFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9FA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9ED7AB"/>
+        <fgColor rgb="FFF7D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -177,19 +279,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
+        <fgColor rgb="FFF6CED1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -201,13 +357,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3606D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
+        <fgColor rgb="FFF4C3C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3CAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA3D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4251"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9CD6A9"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -219,385 +513,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C3C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3606D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C3C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9CD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA3D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4251"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3CAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C3C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFBB2634"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -615,37 +639,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE87C87"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
+        <fgColor rgb="FFDD3E4D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2026,7 +2026,7 @@
       <c r="C2" t="str">
         <v>601107</v>
       </c>
-      <c r="D2" s="11" t="str">
+      <c r="D2" s="13" t="str">
         <v>净买: 2386.11万</v>
       </c>
       <c r="E2">
@@ -2041,41 +2041,41 @@
       <c r="H2">
         <v>-0.18</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="1">
         <v>0.36</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="2">
         <v>1.07</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="3">
         <v>0.18</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="9">
         <v>0.18</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="4">
         <v>-0.54</v>
       </c>
-      <c r="N2" s="12">
+      <c r="N2" s="8">
         <v>0.36</v>
       </c>
-      <c r="O2" s="13">
+      <c r="O2" s="10">
         <v>0.18</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="5">
         <v>1.07</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="11">
         <v>1.07</v>
       </c>
-      <c r="R2" s="3">
+      <c r="R2" s="6">
         <v>0.89</v>
       </c>
-      <c r="S2" s="8">
+      <c r="S2" s="7">
         <v>1.61</v>
       </c>
-      <c r="T2" s="5">
-        <v>8.75</v>
+      <c r="T2" s="12">
+        <v>10.18</v>
       </c>
     </row>
     <row r="3">
@@ -2088,7 +2088,7 @@
       <c r="C3" t="str">
         <v>688755</v>
       </c>
-      <c r="D3" s="17" t="str">
+      <c r="D3" s="25" t="str">
         <v>净买: 1006.54万</v>
       </c>
       <c r="E3">
@@ -2103,41 +2103,41 @@
       <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="16">
         <v>-0.04</v>
       </c>
-      <c r="J3" s="26">
+      <c r="J3" s="17">
         <v>1.4</v>
       </c>
-      <c r="K3" s="24">
+      <c r="K3" s="26">
         <v>1.01</v>
       </c>
-      <c r="L3" s="21">
+      <c r="L3" s="19">
         <v>2.08</v>
       </c>
-      <c r="M3" s="19">
+      <c r="M3" s="20">
         <v>0.13</v>
       </c>
-      <c r="N3" s="14">
+      <c r="N3" s="24">
         <v>0.11</v>
       </c>
-      <c r="O3" s="25">
+      <c r="O3" s="18">
         <v>-0.48</v>
       </c>
-      <c r="P3" s="22">
+      <c r="P3" s="21">
         <v>-2.25</v>
       </c>
-      <c r="Q3" s="15">
+      <c r="Q3" s="22">
         <v>-2.61</v>
       </c>
-      <c r="R3" s="16">
+      <c r="R3" s="14">
         <v>-2.15</v>
       </c>
-      <c r="S3" s="20">
+      <c r="S3" s="23">
         <v>-2.01</v>
       </c>
-      <c r="T3" s="23">
-        <v>-15.61</v>
+      <c r="T3" s="15">
+        <v>-16.55</v>
       </c>
     </row>
     <row r="4">
@@ -2150,7 +2150,7 @@
       <c r="C4" t="str">
         <v>688719</v>
       </c>
-      <c r="D4" s="34" t="str">
+      <c r="D4" s="32" t="str">
         <v>净买: 9087.83万</v>
       </c>
       <c r="E4">
@@ -2165,41 +2165,41 @@
       <c r="H4">
         <v>-1.27</v>
       </c>
-      <c r="I4" s="35">
+      <c r="I4" s="29">
         <v>14.77</v>
       </c>
-      <c r="J4" s="39">
+      <c r="J4" s="38">
         <v>16.43</v>
       </c>
-      <c r="K4" s="36">
+      <c r="K4" s="39">
         <v>15.22</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="33">
         <v>19.4</v>
       </c>
-      <c r="M4" s="37">
+      <c r="M4" s="34">
         <v>29.05</v>
       </c>
-      <c r="N4" s="38">
+      <c r="N4" s="35">
         <v>28.01</v>
       </c>
-      <c r="O4" s="29">
+      <c r="O4" s="27">
         <v>5.89</v>
       </c>
-      <c r="P4" s="30">
+      <c r="P4" s="36">
         <v>21.83</v>
       </c>
-      <c r="Q4" s="27">
+      <c r="Q4" s="30">
         <v>28.6</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="28">
         <v>16.64</v>
       </c>
-      <c r="S4" s="33">
+      <c r="S4" s="31">
         <v>10.06</v>
       </c>
-      <c r="T4" s="31">
-        <v>45.75</v>
+      <c r="T4" s="37">
+        <v>44.54</v>
       </c>
     </row>
     <row r="5">
@@ -2212,7 +2212,7 @@
       <c r="C5" t="str">
         <v>603496</v>
       </c>
-      <c r="D5" s="52" t="str">
+      <c r="D5" s="44" t="str">
         <v>净买: 3657.24万</v>
       </c>
       <c r="E5">
@@ -2227,41 +2227,41 @@
       <c r="H5">
         <v>10.01</v>
       </c>
-      <c r="I5" s="40">
+      <c r="I5" s="50">
         <v>0</v>
       </c>
-      <c r="J5" s="44">
+      <c r="J5" s="41">
         <v>1.21</v>
       </c>
-      <c r="K5" s="47">
+      <c r="K5" s="51">
         <v>8.48</v>
       </c>
-      <c r="L5" s="41">
+      <c r="L5" s="45">
         <v>-2.37</v>
       </c>
-      <c r="M5" s="42">
+      <c r="M5" s="46">
         <v>-7.81</v>
       </c>
-      <c r="N5" s="48">
+      <c r="N5" s="47">
         <v>-10.99</v>
       </c>
-      <c r="O5" s="45">
+      <c r="O5" s="52">
         <v>-12.99</v>
       </c>
-      <c r="P5" s="49">
+      <c r="P5" s="40">
         <v>-13.07</v>
       </c>
-      <c r="Q5" s="50">
+      <c r="Q5" s="42">
         <v>-13.38</v>
       </c>
-      <c r="R5" s="43">
+      <c r="R5" s="48">
         <v>-11.41</v>
       </c>
-      <c r="S5" s="46">
+      <c r="S5" s="49">
         <v>-13.52</v>
       </c>
-      <c r="T5" s="51">
-        <v>-16.17</v>
+      <c r="T5" s="43">
+        <v>-19.3</v>
       </c>
     </row>
     <row r="6">
@@ -2274,7 +2274,7 @@
       <c r="C6" t="str">
         <v>600307</v>
       </c>
-      <c r="D6" s="59" t="str">
+      <c r="D6" s="64" t="str">
         <v>净买: 502.19万</v>
       </c>
       <c r="E6">
@@ -2289,41 +2289,41 @@
       <c r="H6">
         <v>2</v>
       </c>
-      <c r="I6" s="53">
+      <c r="I6" s="65">
         <v>7.84</v>
       </c>
-      <c r="J6" s="54">
+      <c r="J6" s="60">
         <v>18.63</v>
       </c>
-      <c r="K6" s="55">
+      <c r="K6" s="53">
         <v>11.76</v>
       </c>
-      <c r="L6" s="60">
+      <c r="L6" s="54">
         <v>4.41</v>
       </c>
       <c r="M6" s="61">
         <v>1.47</v>
       </c>
-      <c r="N6" s="56">
+      <c r="N6" s="55">
         <v>5.88</v>
       </c>
-      <c r="O6" s="57">
+      <c r="O6" s="56">
         <v>6.86</v>
       </c>
       <c r="P6" s="62">
         <v>2.45</v>
       </c>
-      <c r="Q6" s="63">
+      <c r="Q6" s="57">
         <v>4.41</v>
       </c>
       <c r="R6" s="58">
         <v>3.92</v>
       </c>
-      <c r="S6" s="64">
+      <c r="S6" s="63">
         <v>-1.47</v>
       </c>
-      <c r="T6" s="65">
-        <v>-10.78</v>
+      <c r="T6" s="59">
+        <v>-11.27</v>
       </c>
     </row>
     <row r="7">
@@ -2336,7 +2336,7 @@
       <c r="C7" t="str">
         <v>688566</v>
       </c>
-      <c r="D7" s="73" t="str">
+      <c r="D7" s="66" t="str">
         <v>净买: 36.33万</v>
       </c>
       <c r="E7">
@@ -2351,41 +2351,41 @@
       <c r="H7">
         <v>-1.02</v>
       </c>
-      <c r="I7" s="74">
+      <c r="I7" s="67">
         <v>-0.57</v>
       </c>
-      <c r="J7" s="66">
+      <c r="J7" s="71">
         <v>-1.27</v>
       </c>
-      <c r="K7" s="75">
+      <c r="K7" s="77">
         <v>-6.47</v>
       </c>
-      <c r="L7" s="76">
+      <c r="L7" s="68">
         <v>-4.53</v>
       </c>
-      <c r="M7" s="77">
+      <c r="M7" s="69">
         <v>-3.73</v>
       </c>
-      <c r="N7" s="69">
+      <c r="N7" s="70">
         <v>-4</v>
       </c>
-      <c r="O7" s="78">
+      <c r="O7" s="74">
         <v>-1.03</v>
       </c>
-      <c r="P7" s="67">
+      <c r="P7" s="78">
         <v>-2.3</v>
       </c>
-      <c r="Q7" s="68">
+      <c r="Q7" s="72">
         <v>-2.13</v>
       </c>
-      <c r="R7" s="70">
+      <c r="R7" s="73">
         <v>4.67</v>
       </c>
-      <c r="S7" s="72">
+      <c r="S7" s="75">
         <v>8.87</v>
       </c>
-      <c r="T7" s="71">
-        <v>3.4</v>
+      <c r="T7" s="76">
+        <v>3.83</v>
       </c>
     </row>
     <row r="8">
@@ -2447,40 +2447,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="80">
+      <c r="I9" s="85">
         <v>50</v>
       </c>
-      <c r="J9" s="85">
+      <c r="J9" s="86">
         <v>83.33</v>
       </c>
-      <c r="K9" s="86">
+      <c r="K9" s="79">
         <v>83.33</v>
       </c>
-      <c r="L9" s="88">
+      <c r="L9" s="87">
         <v>66.67</v>
       </c>
-      <c r="M9" s="79">
+      <c r="M9" s="82">
         <v>50</v>
       </c>
-      <c r="N9" s="81">
+      <c r="N9" s="90">
         <v>66.67</v>
       </c>
-      <c r="O9" s="82">
+      <c r="O9" s="83">
         <v>50</v>
       </c>
-      <c r="P9" s="89">
+      <c r="P9" s="88">
         <v>50</v>
       </c>
-      <c r="Q9" s="90">
+      <c r="Q9" s="84">
         <v>50</v>
       </c>
-      <c r="R9" s="83">
+      <c r="R9" s="89">
         <v>66.67</v>
       </c>
-      <c r="S9" s="87">
+      <c r="S9" s="80">
         <v>50</v>
       </c>
-      <c r="T9" s="84">
+      <c r="T9" s="81">
         <v>50</v>
       </c>
     </row>
@@ -2495,41 +2495,41 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="93">
+      <c r="I10" s="91">
         <v>3.73</v>
       </c>
-      <c r="J10" s="94">
+      <c r="J10" s="97">
         <v>6.24</v>
       </c>
-      <c r="K10" s="97">
+      <c r="K10" s="94">
         <v>5.03</v>
       </c>
-      <c r="L10" s="95">
+      <c r="L10" s="99">
         <v>3.2</v>
       </c>
-      <c r="M10" s="91">
+      <c r="M10" s="95">
         <v>3.1</v>
       </c>
-      <c r="N10" s="100">
+      <c r="N10" s="98">
         <v>3.23</v>
       </c>
-      <c r="O10" s="96">
+      <c r="O10" s="100">
         <v>-0.26</v>
       </c>
       <c r="P10" s="101">
         <v>1.29</v>
       </c>
-      <c r="Q10" s="98">
+      <c r="Q10" s="92">
         <v>2.66</v>
       </c>
-      <c r="R10" s="102">
+      <c r="R10" s="93">
         <v>2.09</v>
       </c>
-      <c r="S10" s="92">
+      <c r="S10" s="96">
         <v>0.59</v>
       </c>
-      <c r="T10" s="99">
-        <v>2.56</v>
+      <c r="T10" s="102">
+        <v>1.91</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/中信总部/index.xlsx
+++ b/youzi/中信总部/index.xlsx
@@ -39,31 +39,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFCF0F1"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D7"/>
+        <fgColor rgb="FFF3BDC3"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -75,31 +111,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFCF0F1"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D7"/>
+        <fgColor rgb="FFFDFEFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF9FA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9ED7AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED19D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,13 +207,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,55 +285,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDFEFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9FA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9ED7AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ED19D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CED1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -189,7 +351,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7D6D9"/>
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C3C8"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -207,25 +387,253 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3606D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4251"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3CAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA3D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9CD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF58BA6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C87"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C3C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -238,414 +646,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3606D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C3C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3CAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA3D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4251"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9CD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C3C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C87"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3E4D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2026,7 +2026,7 @@
       <c r="C2" t="str">
         <v>601107</v>
       </c>
-      <c r="D2" s="13" t="str">
+      <c r="D2" s="5" t="str">
         <v>净买: 2386.11万</v>
       </c>
       <c r="E2">
@@ -2041,41 +2041,41 @@
       <c r="H2">
         <v>-0.18</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="13">
         <v>0.36</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="6">
         <v>1.07</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="7">
         <v>0.18</v>
       </c>
-      <c r="L2" s="9">
+      <c r="L2" s="8">
         <v>0.18</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2" s="9">
         <v>-0.54</v>
       </c>
-      <c r="N2" s="8">
+      <c r="N2" s="10">
         <v>0.36</v>
       </c>
-      <c r="O2" s="10">
+      <c r="O2" s="1">
         <v>0.18</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="2">
         <v>1.07</v>
       </c>
-      <c r="Q2" s="11">
+      <c r="Q2" s="3">
         <v>1.07</v>
       </c>
-      <c r="R2" s="6">
+      <c r="R2" s="12">
         <v>0.89</v>
       </c>
-      <c r="S2" s="7">
+      <c r="S2" s="11">
         <v>1.61</v>
       </c>
-      <c r="T2" s="12">
-        <v>10.18</v>
+      <c r="T2" s="4">
+        <v>11.07</v>
       </c>
     </row>
     <row r="3">
@@ -2088,7 +2088,7 @@
       <c r="C3" t="str">
         <v>688755</v>
       </c>
-      <c r="D3" s="25" t="str">
+      <c r="D3" s="19" t="str">
         <v>净买: 1006.54万</v>
       </c>
       <c r="E3">
@@ -2103,41 +2103,41 @@
       <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="14">
         <v>-0.04</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="20">
         <v>1.4</v>
       </c>
-      <c r="K3" s="26">
+      <c r="K3" s="23">
         <v>1.01</v>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="24">
         <v>2.08</v>
       </c>
-      <c r="M3" s="20">
+      <c r="M3" s="15">
         <v>0.13</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="25">
         <v>0.11</v>
       </c>
-      <c r="O3" s="18">
+      <c r="O3" s="16">
         <v>-0.48</v>
       </c>
-      <c r="P3" s="21">
+      <c r="P3" s="17">
         <v>-2.25</v>
       </c>
-      <c r="Q3" s="22">
+      <c r="Q3" s="26">
         <v>-2.61</v>
       </c>
-      <c r="R3" s="14">
+      <c r="R3" s="18">
         <v>-2.15</v>
       </c>
-      <c r="S3" s="23">
+      <c r="S3" s="21">
         <v>-2.01</v>
       </c>
-      <c r="T3" s="15">
-        <v>-16.55</v>
+      <c r="T3" s="22">
+        <v>-17.91</v>
       </c>
     </row>
     <row r="4">
@@ -2165,41 +2165,41 @@
       <c r="H4">
         <v>-1.27</v>
       </c>
-      <c r="I4" s="29">
+      <c r="I4" s="38">
         <v>14.77</v>
       </c>
-      <c r="J4" s="38">
+      <c r="J4" s="35">
         <v>16.43</v>
       </c>
-      <c r="K4" s="39">
+      <c r="K4" s="30">
         <v>15.22</v>
       </c>
-      <c r="L4" s="33">
+      <c r="L4" s="39">
         <v>19.4</v>
       </c>
-      <c r="M4" s="34">
+      <c r="M4" s="33">
         <v>29.05</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="36">
         <v>28.01</v>
       </c>
       <c r="O4" s="27">
         <v>5.89</v>
       </c>
-      <c r="P4" s="36">
+      <c r="P4" s="28">
         <v>21.83</v>
       </c>
-      <c r="Q4" s="30">
+      <c r="Q4" s="34">
         <v>28.6</v>
       </c>
-      <c r="R4" s="28">
+      <c r="R4" s="31">
         <v>16.64</v>
       </c>
-      <c r="S4" s="31">
+      <c r="S4" s="37">
         <v>10.06</v>
       </c>
-      <c r="T4" s="37">
-        <v>44.54</v>
+      <c r="T4" s="29">
+        <v>47.54</v>
       </c>
     </row>
     <row r="5">
@@ -2212,7 +2212,7 @@
       <c r="C5" t="str">
         <v>603496</v>
       </c>
-      <c r="D5" s="44" t="str">
+      <c r="D5" s="52" t="str">
         <v>净买: 3657.24万</v>
       </c>
       <c r="E5">
@@ -2227,41 +2227,41 @@
       <c r="H5">
         <v>10.01</v>
       </c>
-      <c r="I5" s="50">
+      <c r="I5" s="40">
         <v>0</v>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="45">
         <v>1.21</v>
       </c>
-      <c r="K5" s="51">
+      <c r="K5" s="46">
         <v>8.48</v>
       </c>
-      <c r="L5" s="45">
+      <c r="L5" s="44">
         <v>-2.37</v>
       </c>
-      <c r="M5" s="46">
+      <c r="M5" s="48">
         <v>-7.81</v>
       </c>
-      <c r="N5" s="47">
+      <c r="N5" s="49">
         <v>-10.99</v>
       </c>
-      <c r="O5" s="52">
+      <c r="O5" s="50">
         <v>-12.99</v>
       </c>
-      <c r="P5" s="40">
+      <c r="P5" s="41">
         <v>-13.07</v>
       </c>
-      <c r="Q5" s="42">
+      <c r="Q5" s="47">
         <v>-13.38</v>
       </c>
-      <c r="R5" s="48">
+      <c r="R5" s="42">
         <v>-11.41</v>
       </c>
-      <c r="S5" s="49">
+      <c r="S5" s="43">
         <v>-13.52</v>
       </c>
-      <c r="T5" s="43">
-        <v>-19.3</v>
+      <c r="T5" s="51">
+        <v>-8.71</v>
       </c>
     </row>
     <row r="6">
@@ -2274,7 +2274,7 @@
       <c r="C6" t="str">
         <v>600307</v>
       </c>
-      <c r="D6" s="64" t="str">
+      <c r="D6" s="63" t="str">
         <v>净买: 502.19万</v>
       </c>
       <c r="E6">
@@ -2289,41 +2289,41 @@
       <c r="H6">
         <v>2</v>
       </c>
-      <c r="I6" s="65">
+      <c r="I6" s="55">
         <v>7.84</v>
       </c>
-      <c r="J6" s="60">
+      <c r="J6" s="58">
         <v>18.63</v>
       </c>
-      <c r="K6" s="53">
+      <c r="K6" s="64">
         <v>11.76</v>
       </c>
-      <c r="L6" s="54">
+      <c r="L6" s="61">
         <v>4.41</v>
       </c>
-      <c r="M6" s="61">
+      <c r="M6" s="56">
         <v>1.47</v>
       </c>
-      <c r="N6" s="55">
+      <c r="N6" s="57">
         <v>5.88</v>
       </c>
-      <c r="O6" s="56">
+      <c r="O6" s="65">
         <v>6.86</v>
       </c>
-      <c r="P6" s="62">
+      <c r="P6" s="59">
         <v>2.45</v>
       </c>
-      <c r="Q6" s="57">
+      <c r="Q6" s="60">
         <v>4.41</v>
       </c>
-      <c r="R6" s="58">
+      <c r="R6" s="62">
         <v>3.92</v>
       </c>
-      <c r="S6" s="63">
+      <c r="S6" s="53">
         <v>-1.47</v>
       </c>
-      <c r="T6" s="59">
-        <v>-11.27</v>
+      <c r="T6" s="54">
+        <v>-14.71</v>
       </c>
     </row>
     <row r="7">
@@ -2336,7 +2336,7 @@
       <c r="C7" t="str">
         <v>688566</v>
       </c>
-      <c r="D7" s="66" t="str">
+      <c r="D7" s="67" t="str">
         <v>净买: 36.33万</v>
       </c>
       <c r="E7">
@@ -2351,13 +2351,13 @@
       <c r="H7">
         <v>-1.02</v>
       </c>
-      <c r="I7" s="67">
+      <c r="I7" s="71">
         <v>-0.57</v>
       </c>
-      <c r="J7" s="71">
+      <c r="J7" s="72">
         <v>-1.27</v>
       </c>
-      <c r="K7" s="77">
+      <c r="K7" s="78">
         <v>-6.47</v>
       </c>
       <c r="L7" s="68">
@@ -2366,26 +2366,26 @@
       <c r="M7" s="69">
         <v>-3.73</v>
       </c>
-      <c r="N7" s="70">
+      <c r="N7" s="73">
         <v>-4</v>
       </c>
       <c r="O7" s="74">
         <v>-1.03</v>
       </c>
-      <c r="P7" s="78">
+      <c r="P7" s="75">
         <v>-2.3</v>
       </c>
-      <c r="Q7" s="72">
+      <c r="Q7" s="70">
         <v>-2.13</v>
       </c>
-      <c r="R7" s="73">
+      <c r="R7" s="66">
         <v>4.67</v>
       </c>
-      <c r="S7" s="75">
+      <c r="S7" s="76">
         <v>8.87</v>
       </c>
-      <c r="T7" s="76">
-        <v>3.83</v>
+      <c r="T7" s="77">
+        <v>-3.87</v>
       </c>
     </row>
     <row r="8">
@@ -2450,38 +2450,38 @@
       <c r="I9" s="85">
         <v>50</v>
       </c>
-      <c r="J9" s="86">
+      <c r="J9" s="89">
         <v>83.33</v>
       </c>
-      <c r="K9" s="79">
+      <c r="K9" s="86">
         <v>83.33</v>
       </c>
       <c r="L9" s="87">
         <v>66.67</v>
       </c>
-      <c r="M9" s="82">
+      <c r="M9" s="90">
         <v>50</v>
       </c>
-      <c r="N9" s="90">
+      <c r="N9" s="88">
         <v>66.67</v>
       </c>
-      <c r="O9" s="83">
+      <c r="O9" s="79">
         <v>50</v>
       </c>
-      <c r="P9" s="88">
+      <c r="P9" s="81">
         <v>50</v>
       </c>
-      <c r="Q9" s="84">
+      <c r="Q9" s="82">
         <v>50</v>
       </c>
-      <c r="R9" s="89">
+      <c r="R9" s="80">
         <v>66.67</v>
       </c>
-      <c r="S9" s="80">
+      <c r="S9" s="83">
         <v>50</v>
       </c>
-      <c r="T9" s="81">
-        <v>50</v>
+      <c r="T9" s="84">
+        <v>33.33</v>
       </c>
     </row>
     <row r="10">
@@ -2495,41 +2495,41 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="91">
+      <c r="I10" s="100">
         <v>3.73</v>
       </c>
-      <c r="J10" s="97">
+      <c r="J10" s="101">
         <v>6.24</v>
       </c>
-      <c r="K10" s="94">
+      <c r="K10" s="102">
         <v>5.03</v>
       </c>
-      <c r="L10" s="99">
+      <c r="L10" s="94">
         <v>3.2</v>
       </c>
-      <c r="M10" s="95">
+      <c r="M10" s="97">
         <v>3.1</v>
       </c>
-      <c r="N10" s="98">
+      <c r="N10" s="92">
         <v>3.23</v>
       </c>
-      <c r="O10" s="100">
+      <c r="O10" s="98">
         <v>-0.26</v>
       </c>
-      <c r="P10" s="101">
+      <c r="P10" s="91">
         <v>1.29</v>
       </c>
-      <c r="Q10" s="92">
+      <c r="Q10" s="95">
         <v>2.66</v>
       </c>
-      <c r="R10" s="93">
+      <c r="R10" s="96">
         <v>2.09</v>
       </c>
-      <c r="S10" s="96">
+      <c r="S10" s="93">
         <v>0.59</v>
       </c>
-      <c r="T10" s="102">
-        <v>1.91</v>
+      <c r="T10" s="99">
+        <v>2.24</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/中信总部/index.xlsx
+++ b/youzi/中信总部/index.xlsx
@@ -39,19 +39,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFDF7F8"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D7"/>
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDFEFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9ED7AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED19D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF9FA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -63,85 +201,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDFEFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9FA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9ED7AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -153,13 +321,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
+        <fgColor rgb="FFF6CED1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A6"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -171,25 +345,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ED19D"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C3C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -201,169 +417,211 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE3606D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA3D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3CAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9CD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4251"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C87"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -375,265 +633,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3606D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4251"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3CAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA3D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9CD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF58BA6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C87"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C3C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2026,7 +2026,7 @@
       <c r="C2" t="str">
         <v>601107</v>
       </c>
-      <c r="D2" s="5" t="str">
+      <c r="D2" s="9" t="str">
         <v>净买: 2386.11万</v>
       </c>
       <c r="E2">
@@ -2041,41 +2041,41 @@
       <c r="H2">
         <v>-0.18</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="5">
         <v>0.36</v>
       </c>
       <c r="J2" s="6">
         <v>1.07</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="12">
         <v>0.18</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="10">
         <v>0.18</v>
       </c>
-      <c r="M2" s="9">
+      <c r="M2" s="11">
         <v>-0.54</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="7">
         <v>0.36</v>
       </c>
-      <c r="O2" s="1">
+      <c r="O2" s="13">
         <v>0.18</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="8">
         <v>1.07</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="Q2" s="2">
         <v>1.07</v>
       </c>
-      <c r="R2" s="12">
+      <c r="R2" s="3">
         <v>0.89</v>
       </c>
-      <c r="S2" s="11">
+      <c r="S2" s="4">
         <v>1.61</v>
       </c>
-      <c r="T2" s="4">
-        <v>11.07</v>
+      <c r="T2" s="1">
+        <v>9.29</v>
       </c>
     </row>
     <row r="3">
@@ -2103,41 +2103,41 @@
       <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="15">
         <v>-0.04</v>
       </c>
-      <c r="J3" s="20">
+      <c r="J3" s="16">
         <v>1.4</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="25">
         <v>1.01</v>
       </c>
-      <c r="L3" s="24">
+      <c r="L3" s="17">
         <v>2.08</v>
       </c>
-      <c r="M3" s="15">
+      <c r="M3" s="26">
         <v>0.13</v>
       </c>
-      <c r="N3" s="25">
+      <c r="N3" s="18">
         <v>0.11</v>
       </c>
-      <c r="O3" s="16">
+      <c r="O3" s="22">
         <v>-0.48</v>
       </c>
-      <c r="P3" s="17">
+      <c r="P3" s="20">
         <v>-2.25</v>
       </c>
-      <c r="Q3" s="26">
+      <c r="Q3" s="23">
         <v>-2.61</v>
       </c>
-      <c r="R3" s="18">
+      <c r="R3" s="14">
         <v>-2.15</v>
       </c>
-      <c r="S3" s="21">
+      <c r="S3" s="24">
         <v>-2.01</v>
       </c>
-      <c r="T3" s="22">
-        <v>-17.91</v>
+      <c r="T3" s="21">
+        <v>-14.51</v>
       </c>
     </row>
     <row r="4">
@@ -2150,7 +2150,7 @@
       <c r="C4" t="str">
         <v>688719</v>
       </c>
-      <c r="D4" s="32" t="str">
+      <c r="D4" s="37" t="str">
         <v>净买: 9087.83万</v>
       </c>
       <c r="E4">
@@ -2165,41 +2165,41 @@
       <c r="H4">
         <v>-1.27</v>
       </c>
-      <c r="I4" s="38">
+      <c r="I4" s="29">
         <v>14.77</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="30">
         <v>16.43</v>
       </c>
-      <c r="K4" s="30">
+      <c r="K4" s="31">
         <v>15.22</v>
       </c>
-      <c r="L4" s="39">
+      <c r="L4" s="38">
         <v>19.4</v>
       </c>
-      <c r="M4" s="33">
+      <c r="M4" s="39">
         <v>29.05</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="32">
         <v>28.01</v>
       </c>
-      <c r="O4" s="27">
+      <c r="O4" s="34">
         <v>5.89</v>
       </c>
-      <c r="P4" s="28">
+      <c r="P4" s="27">
         <v>21.83</v>
       </c>
-      <c r="Q4" s="34">
+      <c r="Q4" s="33">
         <v>28.6</v>
       </c>
-      <c r="R4" s="31">
+      <c r="R4" s="35">
         <v>16.64</v>
       </c>
-      <c r="S4" s="37">
+      <c r="S4" s="28">
         <v>10.06</v>
       </c>
-      <c r="T4" s="29">
-        <v>47.54</v>
+      <c r="T4" s="36">
+        <v>65.25</v>
       </c>
     </row>
     <row r="5">
@@ -2212,7 +2212,7 @@
       <c r="C5" t="str">
         <v>603496</v>
       </c>
-      <c r="D5" s="52" t="str">
+      <c r="D5" s="47" t="str">
         <v>净买: 3657.24万</v>
       </c>
       <c r="E5">
@@ -2227,41 +2227,41 @@
       <c r="H5">
         <v>10.01</v>
       </c>
-      <c r="I5" s="40">
+      <c r="I5" s="41">
         <v>0</v>
       </c>
-      <c r="J5" s="45">
+      <c r="J5" s="48">
         <v>1.21</v>
       </c>
-      <c r="K5" s="46">
+      <c r="K5" s="49">
         <v>8.48</v>
       </c>
-      <c r="L5" s="44">
+      <c r="L5" s="50">
         <v>-2.37</v>
       </c>
-      <c r="M5" s="48">
+      <c r="M5" s="40">
         <v>-7.81</v>
       </c>
-      <c r="N5" s="49">
+      <c r="N5" s="42">
         <v>-10.99</v>
       </c>
-      <c r="O5" s="50">
+      <c r="O5" s="43">
         <v>-12.99</v>
       </c>
-      <c r="P5" s="41">
+      <c r="P5" s="44">
         <v>-13.07</v>
       </c>
-      <c r="Q5" s="47">
+      <c r="Q5" s="45">
         <v>-13.38</v>
       </c>
-      <c r="R5" s="42">
+      <c r="R5" s="51">
         <v>-11.41</v>
       </c>
-      <c r="S5" s="43">
+      <c r="S5" s="46">
         <v>-13.52</v>
       </c>
-      <c r="T5" s="51">
-        <v>-8.71</v>
+      <c r="T5" s="52">
+        <v>-12.26</v>
       </c>
     </row>
     <row r="6">
@@ -2274,7 +2274,7 @@
       <c r="C6" t="str">
         <v>600307</v>
       </c>
-      <c r="D6" s="63" t="str">
+      <c r="D6" s="65" t="str">
         <v>净买: 502.19万</v>
       </c>
       <c r="E6">
@@ -2289,41 +2289,41 @@
       <c r="H6">
         <v>2</v>
       </c>
-      <c r="I6" s="55">
+      <c r="I6" s="53">
         <v>7.84</v>
       </c>
-      <c r="J6" s="58">
+      <c r="J6" s="62">
         <v>18.63</v>
       </c>
-      <c r="K6" s="64">
+      <c r="K6" s="54">
         <v>11.76</v>
       </c>
-      <c r="L6" s="61">
+      <c r="L6" s="55">
         <v>4.41</v>
       </c>
       <c r="M6" s="56">
         <v>1.47</v>
       </c>
-      <c r="N6" s="57">
+      <c r="N6" s="63">
         <v>5.88</v>
       </c>
-      <c r="O6" s="65">
+      <c r="O6" s="57">
         <v>6.86</v>
       </c>
-      <c r="P6" s="59">
+      <c r="P6" s="61">
         <v>2.45</v>
       </c>
-      <c r="Q6" s="60">
+      <c r="Q6" s="58">
         <v>4.41</v>
       </c>
-      <c r="R6" s="62">
+      <c r="R6" s="64">
         <v>3.92</v>
       </c>
-      <c r="S6" s="53">
+      <c r="S6" s="59">
         <v>-1.47</v>
       </c>
-      <c r="T6" s="54">
-        <v>-14.71</v>
+      <c r="T6" s="60">
+        <v>-14.22</v>
       </c>
     </row>
     <row r="7">
@@ -2336,7 +2336,7 @@
       <c r="C7" t="str">
         <v>688566</v>
       </c>
-      <c r="D7" s="67" t="str">
+      <c r="D7" s="71" t="str">
         <v>净买: 36.33万</v>
       </c>
       <c r="E7">
@@ -2351,41 +2351,41 @@
       <c r="H7">
         <v>-1.02</v>
       </c>
-      <c r="I7" s="71">
+      <c r="I7" s="68">
         <v>-0.57</v>
       </c>
-      <c r="J7" s="72">
+      <c r="J7" s="69">
         <v>-1.27</v>
       </c>
-      <c r="K7" s="78">
+      <c r="K7" s="72">
         <v>-6.47</v>
       </c>
-      <c r="L7" s="68">
+      <c r="L7" s="70">
         <v>-4.53</v>
       </c>
-      <c r="M7" s="69">
+      <c r="M7" s="73">
         <v>-3.73</v>
       </c>
-      <c r="N7" s="73">
+      <c r="N7" s="74">
         <v>-4</v>
       </c>
-      <c r="O7" s="74">
+      <c r="O7" s="75">
         <v>-1.03</v>
       </c>
-      <c r="P7" s="75">
+      <c r="P7" s="76">
         <v>-2.3</v>
       </c>
-      <c r="Q7" s="70">
+      <c r="Q7" s="67">
         <v>-2.13</v>
       </c>
-      <c r="R7" s="66">
+      <c r="R7" s="78">
         <v>4.67</v>
       </c>
-      <c r="S7" s="76">
+      <c r="S7" s="66">
         <v>8.87</v>
       </c>
       <c r="T7" s="77">
-        <v>-3.87</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="8">
@@ -2447,10 +2447,10 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="85">
+      <c r="I9" s="82">
         <v>50</v>
       </c>
-      <c r="J9" s="89">
+      <c r="J9" s="90">
         <v>83.33</v>
       </c>
       <c r="K9" s="86">
@@ -2459,28 +2459,28 @@
       <c r="L9" s="87">
         <v>66.67</v>
       </c>
-      <c r="M9" s="90">
+      <c r="M9" s="79">
         <v>50</v>
       </c>
-      <c r="N9" s="88">
+      <c r="N9" s="83">
         <v>66.67</v>
       </c>
-      <c r="O9" s="79">
+      <c r="O9" s="84">
         <v>50</v>
       </c>
-      <c r="P9" s="81">
+      <c r="P9" s="80">
         <v>50</v>
       </c>
-      <c r="Q9" s="82">
+      <c r="Q9" s="88">
         <v>50</v>
       </c>
-      <c r="R9" s="80">
+      <c r="R9" s="81">
         <v>66.67</v>
       </c>
-      <c r="S9" s="83">
+      <c r="S9" s="89">
         <v>50</v>
       </c>
-      <c r="T9" s="84">
+      <c r="T9" s="85">
         <v>33.33</v>
       </c>
     </row>
@@ -2495,41 +2495,41 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="100">
+      <c r="I10" s="93">
         <v>3.73</v>
       </c>
-      <c r="J10" s="101">
+      <c r="J10" s="102">
         <v>6.24</v>
       </c>
-      <c r="K10" s="102">
+      <c r="K10" s="95">
         <v>5.03</v>
       </c>
-      <c r="L10" s="94">
+      <c r="L10" s="100">
         <v>3.2</v>
       </c>
-      <c r="M10" s="97">
+      <c r="M10" s="94">
         <v>3.1</v>
       </c>
-      <c r="N10" s="92">
+      <c r="N10" s="96">
         <v>3.23</v>
       </c>
-      <c r="O10" s="98">
+      <c r="O10" s="97">
         <v>-0.26</v>
       </c>
-      <c r="P10" s="91">
+      <c r="P10" s="98">
         <v>1.29</v>
       </c>
-      <c r="Q10" s="95">
+      <c r="Q10" s="91">
         <v>2.66</v>
       </c>
-      <c r="R10" s="96">
+      <c r="R10" s="92">
         <v>2.09</v>
       </c>
-      <c r="S10" s="93">
+      <c r="S10" s="99">
         <v>0.59</v>
       </c>
-      <c r="T10" s="99">
-        <v>2.24</v>
+      <c r="T10" s="101">
+        <v>4.91</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/中信总部/index.xlsx
+++ b/youzi/中信总部/index.xlsx
@@ -39,613 +39,613 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED19D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDFEFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF9FA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9ED7AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CED1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3606D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C3C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4251"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3CAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9CD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA3D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFAE202D"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDFEFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9ED7AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ED19D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9FA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C3C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C3C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04C5A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3606D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA3D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3CAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9CD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4251"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C87"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C87"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C3C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2026,7 +2026,7 @@
       <c r="C2" t="str">
         <v>601107</v>
       </c>
-      <c r="D2" s="9" t="str">
+      <c r="D2" s="10" t="str">
         <v>净买: 2386.11万</v>
       </c>
       <c r="E2">
@@ -2041,41 +2041,41 @@
       <c r="H2">
         <v>-0.18</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="7">
         <v>0.36</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="11">
         <v>1.07</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="8">
         <v>0.18</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L2" s="12">
         <v>0.18</v>
       </c>
-      <c r="M2" s="11">
+      <c r="M2" s="5">
         <v>-0.54</v>
       </c>
-      <c r="N2" s="7">
+      <c r="N2" s="6">
         <v>0.36</v>
       </c>
-      <c r="O2" s="13">
+      <c r="O2" s="9">
         <v>0.18</v>
       </c>
-      <c r="P2" s="8">
+      <c r="P2" s="13">
         <v>1.07</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="1">
         <v>1.07</v>
       </c>
-      <c r="R2" s="3">
+      <c r="R2" s="2">
         <v>0.89</v>
       </c>
-      <c r="S2" s="4">
+      <c r="S2" s="3">
         <v>1.61</v>
       </c>
-      <c r="T2" s="1">
-        <v>9.29</v>
+      <c r="T2" s="4">
+        <v>10.18</v>
       </c>
     </row>
     <row r="3">
@@ -2088,7 +2088,7 @@
       <c r="C3" t="str">
         <v>688755</v>
       </c>
-      <c r="D3" s="19" t="str">
+      <c r="D3" s="18" t="str">
         <v>净买: 1006.54万</v>
       </c>
       <c r="E3">
@@ -2103,41 +2103,41 @@
       <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" s="15">
+      <c r="I3" s="23">
         <v>-0.04</v>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="15">
         <v>1.4</v>
       </c>
-      <c r="K3" s="25">
+      <c r="K3" s="24">
         <v>1.01</v>
       </c>
-      <c r="L3" s="17">
+      <c r="L3" s="19">
         <v>2.08</v>
       </c>
-      <c r="M3" s="26">
+      <c r="M3" s="25">
         <v>0.13</v>
       </c>
-      <c r="N3" s="18">
+      <c r="N3" s="16">
         <v>0.11</v>
       </c>
       <c r="O3" s="22">
         <v>-0.48</v>
       </c>
-      <c r="P3" s="20">
+      <c r="P3" s="26">
         <v>-2.25</v>
       </c>
-      <c r="Q3" s="23">
+      <c r="Q3" s="20">
         <v>-2.61</v>
       </c>
-      <c r="R3" s="14">
+      <c r="R3" s="21">
         <v>-2.15</v>
       </c>
-      <c r="S3" s="24">
+      <c r="S3" s="17">
         <v>-2.01</v>
       </c>
-      <c r="T3" s="21">
-        <v>-14.51</v>
+      <c r="T3" s="14">
+        <v>-13.7</v>
       </c>
     </row>
     <row r="4">
@@ -2150,7 +2150,7 @@
       <c r="C4" t="str">
         <v>688719</v>
       </c>
-      <c r="D4" s="37" t="str">
+      <c r="D4" s="28" t="str">
         <v>净买: 9087.83万</v>
       </c>
       <c r="E4">
@@ -2165,41 +2165,41 @@
       <c r="H4">
         <v>-1.27</v>
       </c>
-      <c r="I4" s="29">
+      <c r="I4" s="38">
         <v>14.77</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="35">
         <v>16.43</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="36">
         <v>15.22</v>
       </c>
-      <c r="L4" s="38">
+      <c r="L4" s="29">
         <v>19.4</v>
       </c>
-      <c r="M4" s="39">
+      <c r="M4" s="30">
         <v>29.05</v>
       </c>
-      <c r="N4" s="32">
+      <c r="N4" s="33">
         <v>28.01</v>
       </c>
-      <c r="O4" s="34">
+      <c r="O4" s="39">
         <v>5.89</v>
       </c>
       <c r="P4" s="27">
         <v>21.83</v>
       </c>
-      <c r="Q4" s="33">
+      <c r="Q4" s="31">
         <v>28.6</v>
       </c>
-      <c r="R4" s="35">
+      <c r="R4" s="37">
         <v>16.64</v>
       </c>
-      <c r="S4" s="28">
+      <c r="S4" s="34">
         <v>10.06</v>
       </c>
-      <c r="T4" s="36">
-        <v>65.25</v>
+      <c r="T4" s="32">
+        <v>60.27</v>
       </c>
     </row>
     <row r="5">
@@ -2212,7 +2212,7 @@
       <c r="C5" t="str">
         <v>603496</v>
       </c>
-      <c r="D5" s="47" t="str">
+      <c r="D5" s="44" t="str">
         <v>净买: 3657.24万</v>
       </c>
       <c r="E5">
@@ -2227,41 +2227,41 @@
       <c r="H5">
         <v>10.01</v>
       </c>
-      <c r="I5" s="41">
+      <c r="I5" s="49">
         <v>0</v>
       </c>
-      <c r="J5" s="48">
+      <c r="J5" s="52">
         <v>1.21</v>
       </c>
-      <c r="K5" s="49">
+      <c r="K5" s="40">
         <v>8.48</v>
       </c>
-      <c r="L5" s="50">
+      <c r="L5" s="45">
         <v>-2.37</v>
       </c>
-      <c r="M5" s="40">
+      <c r="M5" s="50">
         <v>-7.81</v>
       </c>
-      <c r="N5" s="42">
+      <c r="N5" s="41">
         <v>-10.99</v>
       </c>
-      <c r="O5" s="43">
+      <c r="O5" s="46">
         <v>-12.99</v>
       </c>
-      <c r="P5" s="44">
+      <c r="P5" s="47">
         <v>-13.07</v>
       </c>
-      <c r="Q5" s="45">
+      <c r="Q5" s="42">
         <v>-13.38</v>
       </c>
       <c r="R5" s="51">
         <v>-11.41</v>
       </c>
-      <c r="S5" s="46">
+      <c r="S5" s="48">
         <v>-13.52</v>
       </c>
-      <c r="T5" s="52">
-        <v>-12.26</v>
+      <c r="T5" s="43">
+        <v>-16.54</v>
       </c>
     </row>
     <row r="6">
@@ -2292,37 +2292,37 @@
       <c r="I6" s="53">
         <v>7.84</v>
       </c>
-      <c r="J6" s="62">
+      <c r="J6" s="54">
         <v>18.63</v>
       </c>
-      <c r="K6" s="54">
+      <c r="K6" s="58">
         <v>11.76</v>
       </c>
-      <c r="L6" s="55">
+      <c r="L6" s="63">
         <v>4.41</v>
       </c>
-      <c r="M6" s="56">
+      <c r="M6" s="64">
         <v>1.47</v>
       </c>
-      <c r="N6" s="63">
+      <c r="N6" s="62">
         <v>5.88</v>
       </c>
-      <c r="O6" s="57">
+      <c r="O6" s="59">
         <v>6.86</v>
       </c>
-      <c r="P6" s="61">
+      <c r="P6" s="60">
         <v>2.45</v>
       </c>
-      <c r="Q6" s="58">
+      <c r="Q6" s="55">
         <v>4.41</v>
       </c>
-      <c r="R6" s="64">
+      <c r="R6" s="56">
         <v>3.92</v>
       </c>
-      <c r="S6" s="59">
+      <c r="S6" s="57">
         <v>-1.47</v>
       </c>
-      <c r="T6" s="60">
+      <c r="T6" s="61">
         <v>-14.22</v>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       <c r="C7" t="str">
         <v>688566</v>
       </c>
-      <c r="D7" s="71" t="str">
+      <c r="D7" s="70" t="str">
         <v>净买: 36.33万</v>
       </c>
       <c r="E7">
@@ -2351,41 +2351,41 @@
       <c r="H7">
         <v>-1.02</v>
       </c>
-      <c r="I7" s="68">
+      <c r="I7" s="71">
         <v>-0.57</v>
       </c>
-      <c r="J7" s="69">
+      <c r="J7" s="75">
         <v>-1.27</v>
       </c>
       <c r="K7" s="72">
         <v>-6.47</v>
       </c>
-      <c r="L7" s="70">
+      <c r="L7" s="73">
         <v>-4.53</v>
       </c>
-      <c r="M7" s="73">
+      <c r="M7" s="76">
         <v>-3.73</v>
       </c>
-      <c r="N7" s="74">
+      <c r="N7" s="67">
         <v>-4</v>
       </c>
-      <c r="O7" s="75">
+      <c r="O7" s="77">
         <v>-1.03</v>
       </c>
-      <c r="P7" s="76">
+      <c r="P7" s="74">
         <v>-2.3</v>
       </c>
-      <c r="Q7" s="67">
+      <c r="Q7" s="78">
         <v>-2.13</v>
       </c>
-      <c r="R7" s="78">
+      <c r="R7" s="66">
         <v>4.67</v>
       </c>
-      <c r="S7" s="66">
+      <c r="S7" s="68">
         <v>8.87</v>
       </c>
-      <c r="T7" s="77">
-        <v>-4.1</v>
+      <c r="T7" s="69">
+        <v>-6.53</v>
       </c>
     </row>
     <row r="8">
@@ -2447,40 +2447,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="82">
+      <c r="I9" s="80">
         <v>50</v>
       </c>
-      <c r="J9" s="90">
+      <c r="J9" s="89">
         <v>83.33</v>
       </c>
-      <c r="K9" s="86">
+      <c r="K9" s="84">
         <v>83.33</v>
       </c>
-      <c r="L9" s="87">
+      <c r="L9" s="85">
         <v>66.67</v>
       </c>
-      <c r="M9" s="79">
+      <c r="M9" s="81">
         <v>50</v>
       </c>
-      <c r="N9" s="83">
+      <c r="N9" s="86">
         <v>66.67</v>
       </c>
-      <c r="O9" s="84">
+      <c r="O9" s="87">
         <v>50</v>
       </c>
-      <c r="P9" s="80">
+      <c r="P9" s="90">
         <v>50</v>
       </c>
       <c r="Q9" s="88">
         <v>50</v>
       </c>
-      <c r="R9" s="81">
+      <c r="R9" s="82">
         <v>66.67</v>
       </c>
-      <c r="S9" s="89">
+      <c r="S9" s="79">
         <v>50</v>
       </c>
-      <c r="T9" s="85">
+      <c r="T9" s="83">
         <v>33.33</v>
       </c>
     </row>
@@ -2498,38 +2498,38 @@
       <c r="I10" s="93">
         <v>3.73</v>
       </c>
-      <c r="J10" s="102">
+      <c r="J10" s="94">
         <v>6.24</v>
       </c>
-      <c r="K10" s="95">
+      <c r="K10" s="98">
         <v>5.03</v>
       </c>
-      <c r="L10" s="100">
+      <c r="L10" s="95">
         <v>3.2</v>
       </c>
-      <c r="M10" s="94">
+      <c r="M10" s="100">
         <v>3.1</v>
       </c>
       <c r="N10" s="96">
         <v>3.23</v>
       </c>
-      <c r="O10" s="97">
+      <c r="O10" s="99">
         <v>-0.26</v>
       </c>
-      <c r="P10" s="98">
+      <c r="P10" s="101">
         <v>1.29</v>
       </c>
-      <c r="Q10" s="91">
+      <c r="Q10" s="102">
         <v>2.66</v>
       </c>
-      <c r="R10" s="92">
+      <c r="R10" s="91">
         <v>2.09</v>
       </c>
-      <c r="S10" s="99">
+      <c r="S10" s="97">
         <v>0.59</v>
       </c>
-      <c r="T10" s="101">
-        <v>4.91</v>
+      <c r="T10" s="92">
+        <v>3.24</v>
       </c>
     </row>
   </sheetData>
